--- a/Proyecto/Archivos de apoyo/metas.xlsx
+++ b/Proyecto/Archivos de apoyo/metas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanivilleda/Desktop/Programación II/Proyecto/programa-II/Proyecto/Archivos de apoyo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEE6406D-F2AD-1A42-8C49-95B9B4F27F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526373E8-60FA-EC4C-A961-ACE40447295E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="2000" windowWidth="26840" windowHeight="15020" xr2:uid="{740EF855-3F9C-5E4E-A75D-D4CFD83150A9}"/>
+    <workbookView xWindow="1580" yWindow="1960" windowWidth="26840" windowHeight="15020" xr2:uid="{740EF855-3F9C-5E4E-A75D-D4CFD83150A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -127,11 +127,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -452,130 +451,130 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>93</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>91</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>94.39</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>15</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>90.32</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>80.8</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>136.16</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>404.86327950600662</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>14654.86531187161</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>77</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>72</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>83.4</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>18.2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>66.2</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>42.91</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>79.430000000000007</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>404.86327950600662</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>14654.86531187161</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>13.79617391901793</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>4.8722278047002696</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>30.847999194259994</v>
       </c>
-      <c r="E4" s="4">
-        <v>2.062088376111026</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="E4" s="3">
+        <v>83.537911623888974</v>
+      </c>
+      <c r="F4" s="3">
         <v>2.7889299295772521</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>3.438326430937106</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>35.995936132414002</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>8.3739419791410761</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>1168.6910404597584</v>
       </c>
     </row>
